--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CeAssetGroup.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CeAssetGroup.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2775" windowWidth="12495" windowHeight="3105"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13890" windowHeight="2445"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="0"/>
   <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>系列名称</t>
   </si>
@@ -25,10 +25,6 @@
   </si>
   <si>
     <t>授信总额度(亿元)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -47,8 +43,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,6 +91,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -143,7 +142,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -175,9 +174,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -209,6 +209,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -384,9 +385,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="16.375" customWidth="1"/>
@@ -400,12 +401,12 @@
     <col min="12" max="12" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -414,13 +415,10 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
         <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
